--- a/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0979</v>
+        <v>0.12</v>
       </c>
       <c r="E2">
-        <v>0.145</v>
+        <v>0.186</v>
       </c>
       <c r="F2">
-        <v>0.058</v>
+        <v>0.131</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>2031.82</v>
+        <v>1963</v>
       </c>
       <c r="L2">
-        <v>0.3022642070812258</v>
+        <v>0.3015407302723545</v>
       </c>
       <c r="M2">
-        <v>583.7</v>
+        <v>687.65</v>
       </c>
       <c r="N2">
-        <v>0.08692583083640609</v>
+        <v>0.1342961487383798</v>
       </c>
       <c r="O2">
-        <v>0.2872793849848904</v>
+        <v>0.3503056546102903</v>
       </c>
       <c r="P2">
-        <v>581.25</v>
+        <v>681.8200000000001</v>
       </c>
       <c r="Q2">
-        <v>0.08656097168693</v>
+        <v>0.1331575658151707</v>
       </c>
       <c r="R2">
-        <v>0.2860735695091101</v>
+        <v>0.3473357106469689</v>
       </c>
       <c r="S2">
-        <v>2.449999999999989</v>
+        <v>5.830000000000013</v>
       </c>
       <c r="T2">
-        <v>0.004197361658386137</v>
+        <v>0.008478150221769815</v>
       </c>
       <c r="U2">
-        <v>15056.14</v>
+        <v>15258.1</v>
       </c>
       <c r="V2">
-        <v>2.242192014201212</v>
+        <v>2.979864854308258</v>
       </c>
       <c r="W2">
-        <v>0.1263321043152007</v>
+        <v>0.1477239779646274</v>
       </c>
       <c r="X2">
-        <v>0.1552889482995004</v>
+        <v>0.2190161294526885</v>
       </c>
       <c r="Y2">
-        <v>-0.02895684398429965</v>
+        <v>-0.07129215148806103</v>
       </c>
       <c r="Z2">
-        <v>0.5956115074765991</v>
+        <v>0.6530104142216017</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08923512823155016</v>
+        <v>0.1433619701322168</v>
       </c>
       <c r="AC2">
-        <v>-0.08923512823155016</v>
+        <v>-0.1433619701322168</v>
       </c>
       <c r="AD2">
-        <v>12787.4</v>
+        <v>12402.14</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12787.4</v>
+        <v>12402.14</v>
       </c>
       <c r="AG2">
-        <v>-2268.74</v>
+        <v>-2855.960000000001</v>
       </c>
       <c r="AH2">
-        <v>0.6556860927315314</v>
+        <v>0.7077820909525673</v>
       </c>
       <c r="AI2">
-        <v>0.5072271760860597</v>
+        <v>0.5255179696133534</v>
       </c>
       <c r="AJ2">
-        <v>-0.510267240642529</v>
+        <v>-1.261221317411812</v>
       </c>
       <c r="AK2">
-        <v>-0.223427408791975</v>
+        <v>-0.3423698173282794</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guaranty Trust Holding Company Plc (NGSE:GTCO)</t>
+          <t>NPF Microfinance Bank Plc (NGSE:NPFMCRFBK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E3">
-        <v>0.0579</v>
+        <v>-0.0115</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>454.2</v>
+        <v>1.34</v>
       </c>
       <c r="L3">
-        <v>0.4879149210441508</v>
+        <v>0.1072</v>
       </c>
       <c r="M3">
-        <v>196.35</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
-        <v>0.1423548176611324</v>
+        <v>0.05530973451327433</v>
       </c>
       <c r="O3">
-        <v>0.4322985468956407</v>
+        <v>0.9328358208955223</v>
       </c>
       <c r="P3">
-        <v>193.9</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>0.1405785543391576</v>
+        <v>0.05530973451327433</v>
       </c>
       <c r="R3">
-        <v>0.4269044473800088</v>
+        <v>0.9328358208955223</v>
       </c>
       <c r="S3">
-        <v>2.449999999999989</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01247771836007124</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1849.3</v>
+        <v>23.2</v>
       </c>
       <c r="V3">
-        <v>1.340752555644167</v>
+        <v>1.026548672566372</v>
       </c>
       <c r="W3">
-        <v>0.2347286821705426</v>
+        <v>0.0943661971830986</v>
       </c>
       <c r="X3">
-        <v>0.08031545456381564</v>
+        <v>0.1296589057927731</v>
       </c>
       <c r="Y3">
-        <v>0.154413227606727</v>
+        <v>-0.03529270860967446</v>
       </c>
       <c r="Z3">
-        <v>1.231512104775764</v>
+        <v>0.485248447204969</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07425739798663444</v>
+        <v>0.122466470514737</v>
       </c>
       <c r="AC3">
-        <v>-0.07425739798663444</v>
+        <v>-0.122466470514737</v>
       </c>
       <c r="AD3">
-        <v>332.4</v>
+        <v>6.34</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>332.4</v>
+        <v>6.34</v>
       </c>
       <c r="AG3">
-        <v>-1516.9</v>
+        <v>-16.86</v>
       </c>
       <c r="AH3">
-        <v>0.1941929076356838</v>
+        <v>0.2190739460953697</v>
       </c>
       <c r="AI3">
-        <v>0.139172667894825</v>
+        <v>0.2082785808147175</v>
       </c>
       <c r="AJ3">
-        <v>11.02398255813952</v>
+        <v>-2.937282229965156</v>
       </c>
       <c r="AK3">
-        <v>-2.813763680207754</v>
+        <v>-2.328729281767955</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Union Bank of Nigeria Plc (NGSE:UBN)</t>
+          <t>Guaranty Trust Holding Company Plc (NGSE:GTCO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.065</v>
+        <v>0.0694</v>
       </c>
       <c r="E4">
-        <v>-0.009809999999999999</v>
+        <v>0.04269999999999999</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,85 +853,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>41.5</v>
+        <v>398.8</v>
       </c>
       <c r="L4">
-        <v>0.1606658923732094</v>
+        <v>0.4129219300062125</v>
       </c>
       <c r="M4">
-        <v>17.8</v>
+        <v>227.76</v>
       </c>
       <c r="N4">
-        <v>0.04254302103250478</v>
+        <v>0.2082472341592759</v>
       </c>
       <c r="O4">
-        <v>0.4289156626506024</v>
+        <v>0.5711133400200602</v>
       </c>
       <c r="P4">
-        <v>17.8</v>
+        <v>226.4</v>
       </c>
       <c r="Q4">
-        <v>0.04254302103250478</v>
+        <v>0.2070037487427997</v>
       </c>
       <c r="R4">
-        <v>0.4289156626506024</v>
+        <v>0.567703109327984</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.360000000000014</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.00597119775201973</v>
       </c>
       <c r="U4">
-        <v>966.2</v>
+        <v>2729.4</v>
       </c>
       <c r="V4">
-        <v>2.309273422562142</v>
+        <v>2.495565511566243</v>
       </c>
       <c r="W4">
-        <v>0.06207928197456993</v>
+        <v>0.1981516446387757</v>
       </c>
       <c r="X4">
-        <v>0.1300635495848933</v>
+        <v>0.1319961023607807</v>
       </c>
       <c r="Y4">
-        <v>-0.06798426761032339</v>
+        <v>0.06615554227799506</v>
       </c>
       <c r="Z4">
-        <v>0.4202733485193623</v>
+        <v>2.03540569020021</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.08454087580142233</v>
+        <v>0.1233800433941056</v>
       </c>
       <c r="AC4">
-        <v>-0.08454087580142233</v>
+        <v>-0.1233800433941056</v>
       </c>
       <c r="AD4">
-        <v>633.7</v>
+        <v>354.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>633.7</v>
+        <v>354.9</v>
       </c>
       <c r="AG4">
-        <v>-332.5</v>
+        <v>-2374.5</v>
       </c>
       <c r="AH4">
-        <v>0.6023191711814467</v>
+        <v>0.2449951677481707</v>
       </c>
       <c r="AI4">
-        <v>0.4952715904650254</v>
+        <v>0.1494378710682555</v>
       </c>
       <c r="AJ4">
-        <v>-3.870779976717114</v>
+        <v>1.853919425359151</v>
       </c>
       <c r="AK4">
-        <v>-1.061283115225024</v>
+        <v>6.698166431593794</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NPF Microfinance Bank Plc (NGSE:NPFMCRFBK)</t>
+          <t>Union Bank of Nigeria Plc (NGSE:UBN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.153</v>
+        <v>0.0525</v>
       </c>
       <c r="E5">
-        <v>0.0412</v>
+        <v>-0.0406</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,28 +975,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2.04</v>
+        <v>28.1</v>
       </c>
       <c r="L5">
-        <v>0.1658536585365853</v>
+        <v>0.1147875816993464</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>16.9</v>
       </c>
       <c r="N5">
-        <v>0.118895966029724</v>
+        <v>0.04043062200956937</v>
       </c>
       <c r="O5">
-        <v>0.5490196078431373</v>
+        <v>0.6014234875444839</v>
       </c>
       <c r="P5">
-        <v>1.12</v>
+        <v>16.9</v>
       </c>
       <c r="Q5">
-        <v>0.118895966029724</v>
+        <v>0.04043062200956937</v>
       </c>
       <c r="R5">
-        <v>0.5490196078431373</v>
+        <v>0.6014234875444839</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,55 +1005,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>3.24</v>
+        <v>904.4</v>
       </c>
       <c r="V5">
-        <v>0.3439490445859873</v>
+        <v>2.163636363636364</v>
       </c>
       <c r="W5">
-        <v>0.1436619718309859</v>
+        <v>0.04463860206513106</v>
       </c>
       <c r="X5">
-        <v>0.1322723114351573</v>
+        <v>0.1669024194537139</v>
       </c>
       <c r="Y5">
-        <v>0.01138966039582864</v>
+        <v>-0.1222638173885828</v>
       </c>
       <c r="Z5">
-        <v>0.8436213991769549</v>
+        <v>0.8242424242424243</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.08473892138813871</v>
+        <v>0.1321993729804838</v>
       </c>
       <c r="AC5">
-        <v>-0.08473892138813871</v>
+        <v>-0.1321993729804838</v>
       </c>
       <c r="AD5">
-        <v>14.8</v>
+        <v>410.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14.8</v>
+        <v>410.1</v>
       </c>
       <c r="AG5">
-        <v>11.56</v>
+        <v>-494.3</v>
       </c>
       <c r="AH5">
-        <v>0.6110652353426921</v>
+        <v>0.4952300446805942</v>
       </c>
       <c r="AI5">
-        <v>0.5103448275862069</v>
+        <v>0.3960788101216921</v>
       </c>
       <c r="AJ5">
-        <v>0.5510009532888466</v>
+        <v>6.478374836173004</v>
       </c>
       <c r="AK5">
-        <v>0.4487577639751553</v>
+        <v>-3.773282442748091</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FCMB Group Plc (NGSE:FCMB)</t>
+          <t>Wema Bank PLC (NGSE:WEMABANK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0833</v>
+        <v>0.186</v>
       </c>
       <c r="E6">
-        <v>0.198</v>
+        <v>0.31</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,28 +1097,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>47</v>
+        <v>25.2</v>
       </c>
       <c r="L6">
-        <v>0.1696750902527076</v>
+        <v>0.1575</v>
       </c>
       <c r="M6">
-        <v>7.25</v>
+        <v>7.14</v>
       </c>
       <c r="N6">
-        <v>0.05052264808362369</v>
+        <v>0.06380697050938337</v>
       </c>
       <c r="O6">
-        <v>0.1542553191489362</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="P6">
-        <v>7.25</v>
+        <v>7.14</v>
       </c>
       <c r="Q6">
-        <v>0.05052264808362369</v>
+        <v>0.06380697050938337</v>
       </c>
       <c r="R6">
-        <v>0.1542553191489362</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1127,55 +1127,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>882.4</v>
+        <v>247.2</v>
       </c>
       <c r="V6">
-        <v>6.149128919860627</v>
+        <v>2.20911528150134</v>
       </c>
       <c r="W6">
-        <v>0.08383874420264002</v>
+        <v>0.1620578778135048</v>
       </c>
       <c r="X6">
-        <v>0.2690398418611124</v>
+        <v>0.1861503319588135</v>
       </c>
       <c r="Y6">
-        <v>-0.1852010976584724</v>
+        <v>-0.02409245414530869</v>
       </c>
       <c r="Z6">
-        <v>0.2487204812786208</v>
+        <v>1.773835920177383</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08533533789736909</v>
+        <v>0.1349482977027426</v>
       </c>
       <c r="AC6">
-        <v>-0.08533533789736909</v>
+        <v>-0.1349482977027426</v>
       </c>
       <c r="AD6">
-        <v>727.9</v>
+        <v>150.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>727.9</v>
+        <v>150.3</v>
       </c>
       <c r="AG6">
-        <v>-154.5</v>
+        <v>-96.89999999999998</v>
       </c>
       <c r="AH6">
-        <v>0.8353224695891669</v>
+        <v>0.5732265446224256</v>
       </c>
       <c r="AI6">
-        <v>0.5582911489492254</v>
+        <v>0.4633168927250309</v>
       </c>
       <c r="AJ6">
-        <v>14.04545454545454</v>
+        <v>-6.459999999999987</v>
       </c>
       <c r="AK6">
-        <v>-0.3666350261034647</v>
+        <v>-1.255181347150258</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wema Bank PLC (NGSE:WEMABANK)</t>
+          <t>Unity Bank Plc (NGSE:UNITYBNK)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.146</v>
+        <v>0.0277</v>
       </c>
       <c r="E7">
-        <v>0.295</v>
+        <v>0.22</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,85 +1219,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>19.9</v>
+        <v>7.56</v>
       </c>
       <c r="L7">
-        <v>0.1583134447096261</v>
+        <v>0.1067796610169491</v>
       </c>
       <c r="M7">
-        <v>3.77</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.05601783060921248</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.1894472361809045</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>3.77</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.05601783060921248</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.1894472361809045</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>242.6</v>
+        <v>18.1</v>
       </c>
       <c r="V7">
-        <v>3.604754829123328</v>
+        <v>1.265734265734266</v>
       </c>
       <c r="W7">
-        <v>0.1360218728639781</v>
+        <v>-0.01103810775295664</v>
       </c>
       <c r="X7">
-        <v>0.1738081290041786</v>
+        <v>3.842017329789793</v>
       </c>
       <c r="Y7">
-        <v>-0.03778625614020051</v>
+        <v>-3.853055437542749</v>
       </c>
       <c r="Z7">
-        <v>1.181390977443609</v>
+        <v>0.1588868940754039</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.08576970991181966</v>
+        <v>0.141557174994369</v>
       </c>
       <c r="AC7">
-        <v>-0.08576970991181966</v>
+        <v>-0.141557174994369</v>
       </c>
       <c r="AD7">
-        <v>177.3</v>
+        <v>1002.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>177.3</v>
+        <v>1002.6</v>
       </c>
       <c r="AG7">
-        <v>-65.29999999999998</v>
+        <v>984.5</v>
       </c>
       <c r="AH7">
-        <v>0.7248569092395748</v>
+        <v>0.9859376536532599</v>
       </c>
       <c r="AI7">
-        <v>0.5327524038461539</v>
+        <v>2.743091655266758</v>
       </c>
       <c r="AJ7">
-        <v>-32.64999999999976</v>
+        <v>0.98568281938326</v>
       </c>
       <c r="AK7">
-        <v>-0.7239467849223944</v>
+        <v>2.833909038572251</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1323,10 +1320,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0898</v>
+        <v>0.124</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>0.258</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1341,28 +1338,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>32.6</v>
+        <v>40.4</v>
       </c>
       <c r="L8">
-        <v>0.1441202475685235</v>
+        <v>0.1711139347734011</v>
       </c>
       <c r="M8">
-        <v>3.51</v>
+        <v>6.66</v>
       </c>
       <c r="N8">
-        <v>0.03333333333333333</v>
+        <v>0.074</v>
       </c>
       <c r="O8">
-        <v>0.1076687116564417</v>
+        <v>0.1648514851485149</v>
       </c>
       <c r="P8">
-        <v>3.51</v>
+        <v>6.66</v>
       </c>
       <c r="Q8">
-        <v>0.03333333333333333</v>
+        <v>0.074</v>
       </c>
       <c r="R8">
-        <v>0.1076687116564417</v>
+        <v>0.1648514851485149</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1371,55 +1368,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>470.4</v>
+        <v>515.8</v>
       </c>
       <c r="V8">
-        <v>4.467236467236467</v>
+        <v>5.731111111111111</v>
       </c>
       <c r="W8">
-        <v>0.09804511278195489</v>
+        <v>0.1203097081596188</v>
       </c>
       <c r="X8">
-        <v>0.2274071931258639</v>
+        <v>0.3442860847273604</v>
       </c>
       <c r="Y8">
-        <v>-0.1293620803439091</v>
+        <v>-0.2239763765677416</v>
       </c>
       <c r="Z8">
-        <v>0.4541256775747842</v>
+        <v>0.8217890706578487</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.087316436322998</v>
+        <v>0.1433619701322168</v>
       </c>
       <c r="AC8">
-        <v>-0.087316436322998</v>
+        <v>-0.1433619701322168</v>
       </c>
       <c r="AD8">
-        <v>421.9</v>
+        <v>388.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>421.9</v>
+        <v>388.6</v>
       </c>
       <c r="AG8">
-        <v>-48.5</v>
+        <v>-127.1999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.8002655538694993</v>
+        <v>0.8119515252820727</v>
       </c>
       <c r="AI8">
-        <v>0.5568166820641414</v>
+        <v>0.5275590551181103</v>
       </c>
       <c r="AJ8">
-        <v>-0.8538732394366197</v>
+        <v>3.419354838709682</v>
       </c>
       <c r="AK8">
-        <v>-0.1688130873651236</v>
+        <v>-0.5760869565217387</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1436,7 +1433,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unity Bank Plc (NGSE:UNITYBNK)</t>
+          <t>Access Holdings Plc (NGSE:ACCESSCORP)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1445,7 +1442,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0594</v>
+        <v>0.172</v>
+      </c>
+      <c r="E9">
+        <v>0.186</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1460,82 +1460,85 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>5.98</v>
+        <v>399.2</v>
       </c>
       <c r="L9">
-        <v>0.08704512372634643</v>
+        <v>0.2674169346195069</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>83.97</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.1278860798050563</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.2103456913827655</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>79.5</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.1210782820590923</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.1991482965931864</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>4.469999999999999</v>
+      </c>
+      <c r="T9">
+        <v>0.05323329760628795</v>
       </c>
       <c r="U9">
-        <v>63.9</v>
+        <v>2758.6</v>
       </c>
       <c r="V9">
-        <v>4.176470588235293</v>
+        <v>4.201340237587572</v>
       </c>
       <c r="W9">
-        <v>-0.008223322332233223</v>
+        <v>0.2091914269244878</v>
       </c>
       <c r="X9">
-        <v>3.120243145981736</v>
+        <v>0.4123573656721677</v>
       </c>
       <c r="Y9">
-        <v>-3.12846646831397</v>
+        <v>-0.20316593874768</v>
       </c>
       <c r="Z9">
-        <v>0.5768261964735519</v>
+        <v>0.58994625355675</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.09115382014010234</v>
+        <v>0.1446481283129669</v>
       </c>
       <c r="AC9">
-        <v>-0.09115382014010234</v>
+        <v>-0.1446481283129669</v>
       </c>
       <c r="AD9">
-        <v>1194.4</v>
+        <v>3675.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1194.4</v>
+        <v>3675.8</v>
       </c>
       <c r="AG9">
-        <v>1130.5</v>
+        <v>917.2000000000003</v>
       </c>
       <c r="AH9">
-        <v>0.9873522360915929</v>
+        <v>0.8484442803065275</v>
       </c>
       <c r="AI9">
-        <v>2.344259077526987</v>
+        <v>0.6055184910633391</v>
       </c>
       <c r="AJ9">
-        <v>0.9866468842729971</v>
+        <v>0.58279323929343</v>
       </c>
       <c r="AK9">
-        <v>2.537028725314183</v>
+        <v>0.2769407288867418</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1552,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FBN Holdings Plc (NGSE:FBNH)</t>
+          <t>FCMB Group Plc (NGSE:FCMB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1561,13 +1564,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="E10">
-        <v>0.508</v>
-      </c>
-      <c r="F10">
-        <v>0.05</v>
+        <v>0.341</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1582,28 +1582,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>149.2</v>
+        <v>68.5</v>
       </c>
       <c r="L10">
-        <v>0.1586221560705932</v>
+        <v>0.2065119083509195</v>
       </c>
       <c r="M10">
-        <v>39.4</v>
+        <v>9.17</v>
       </c>
       <c r="N10">
-        <v>0.03973777105395865</v>
+        <v>0.05387779083431258</v>
       </c>
       <c r="O10">
-        <v>0.2640750670241287</v>
+        <v>0.1338686131386861</v>
       </c>
       <c r="P10">
-        <v>39.4</v>
+        <v>9.17</v>
       </c>
       <c r="Q10">
-        <v>0.03973777105395865</v>
+        <v>0.05387779083431258</v>
       </c>
       <c r="R10">
-        <v>0.2640750670241287</v>
+        <v>0.1338686131386861</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1612,55 +1612,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>3046.4</v>
+        <v>703.1</v>
       </c>
       <c r="V10">
-        <v>3.072516389309128</v>
+        <v>4.131022326674501</v>
       </c>
       <c r="W10">
-        <v>0.08117077416897883</v>
+        <v>0.1191926222376892</v>
       </c>
       <c r="X10">
-        <v>0.1154906613063072</v>
+        <v>0.4320917787956251</v>
       </c>
       <c r="Y10">
-        <v>-0.03431988713732839</v>
+        <v>-0.3128991565579359</v>
       </c>
       <c r="Z10">
-        <v>-1.456488076803964</v>
+        <v>0.845095541401274</v>
       </c>
       <c r="AA10">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.0942588840611811</v>
+        <v>0.1449326310820667</v>
       </c>
       <c r="AC10">
-        <v>-0.0942588840611811</v>
+        <v>-0.1449326310820667</v>
       </c>
       <c r="AD10">
-        <v>1131.8</v>
+        <v>1016</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1131.8</v>
+        <v>1016</v>
       </c>
       <c r="AG10">
-        <v>-1914.6</v>
+        <v>312.9</v>
       </c>
       <c r="AH10">
-        <v>0.533038195262092</v>
+        <v>0.8565166076546956</v>
       </c>
       <c r="AI10">
-        <v>0.3809748215968762</v>
+        <v>0.624923114774265</v>
       </c>
       <c r="AJ10">
-        <v>2.074098147546311</v>
+        <v>0.647691989236183</v>
       </c>
       <c r="AK10">
-        <v>25.32539682539678</v>
+        <v>0.3391134713341281</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.106</v>
+        <v>0.0989</v>
       </c>
       <c r="E11">
-        <v>0.145</v>
+        <v>0.096</v>
       </c>
       <c r="F11">
-        <v>0.066</v>
+        <v>0.131</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1707,28 +1707,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>565.4</v>
+        <v>597.5</v>
       </c>
       <c r="L11">
-        <v>0.4314054631466504</v>
+        <v>0.41045545098578</v>
       </c>
       <c r="M11">
-        <v>230</v>
+        <v>225.4</v>
       </c>
       <c r="N11">
-        <v>0.1202111535044165</v>
+        <v>0.1340230705196813</v>
       </c>
       <c r="O11">
-        <v>0.4067916519278387</v>
+        <v>0.3772384937238494</v>
       </c>
       <c r="P11">
-        <v>230</v>
+        <v>225.4</v>
       </c>
       <c r="Q11">
-        <v>0.1202111535044165</v>
+        <v>0.1340230705196813</v>
       </c>
       <c r="R11">
-        <v>0.4067916519278387</v>
+        <v>0.3772384937238494</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1737,55 +1737,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2376.7</v>
+        <v>4418</v>
       </c>
       <c r="V11">
-        <v>1.242199341451942</v>
+        <v>2.626947318349388</v>
       </c>
       <c r="W11">
-        <v>0.2093918968965262</v>
+        <v>0.206447377513648</v>
       </c>
       <c r="X11">
-        <v>0.1226701074331819</v>
+        <v>0.216804725042037</v>
       </c>
       <c r="Y11">
-        <v>0.08672178946334425</v>
+        <v>-0.01035734752838902</v>
       </c>
       <c r="Z11">
-        <v>0.3923717142686066</v>
+        <v>0.4767784619415695</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.09587622749988467</v>
+        <v>0.1626345597320497</v>
       </c>
       <c r="AC11">
-        <v>-0.09587622749988467</v>
+        <v>-0.1626345597320497</v>
       </c>
       <c r="AD11">
-        <v>2535.7</v>
+        <v>3228.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>2535.7</v>
+        <v>3228.7</v>
       </c>
       <c r="AG11">
-        <v>159</v>
+        <v>-1189.3</v>
       </c>
       <c r="AH11">
-        <v>0.5699483029894358</v>
+        <v>0.6575094185928113</v>
       </c>
       <c r="AI11">
-        <v>0.4667562493097227</v>
+        <v>0.5159810784031706</v>
       </c>
       <c r="AJ11">
-        <v>0.07672634271099743</v>
+        <v>-2.414822335025382</v>
       </c>
       <c r="AK11">
-        <v>0.0520304983801826</v>
+        <v>-0.6465695335435471</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.145</v>
+        <v>0.114</v>
       </c>
       <c r="E12">
-        <v>0.182</v>
+        <v>0.0953</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1829,28 +1829,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>332</v>
+        <v>294.5</v>
       </c>
       <c r="L12">
-        <v>0.3190160468915153</v>
+        <v>0.2531373560254426</v>
       </c>
       <c r="M12">
-        <v>45.9</v>
+        <v>79.2</v>
       </c>
       <c r="N12">
-        <v>0.0648671565856416</v>
+        <v>0.1365281847957249</v>
       </c>
       <c r="O12">
-        <v>0.1382530120481928</v>
+        <v>0.2689303904923599</v>
       </c>
       <c r="P12">
-        <v>45.9</v>
+        <v>79.2</v>
       </c>
       <c r="Q12">
-        <v>0.0648671565856416</v>
+        <v>0.1365281847957249</v>
       </c>
       <c r="R12">
-        <v>0.1382530120481928</v>
+        <v>0.2689303904923599</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1859,55 +1859,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1424.6</v>
+        <v>2207.2</v>
       </c>
       <c r="V12">
-        <v>2.013284341435839</v>
+        <v>3.804861230822271</v>
       </c>
       <c r="W12">
-        <v>0.2021432050657574</v>
+        <v>0.1573856348867037</v>
       </c>
       <c r="X12">
-        <v>0.1367697675948222</v>
+        <v>0.2190161294526885</v>
       </c>
       <c r="Y12">
-        <v>0.06537343747093527</v>
+        <v>-0.06163049456598477</v>
       </c>
       <c r="Z12">
-        <v>0.5136469078525245</v>
+        <v>0.7094767654592024</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.09840838081390259</v>
+        <v>0.1629849546214148</v>
       </c>
       <c r="AC12">
-        <v>-0.09840838081390259</v>
+        <v>-0.1629849546214148</v>
       </c>
       <c r="AD12">
-        <v>1193.2</v>
+        <v>1137.8</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1193.2</v>
+        <v>1137.8</v>
       </c>
       <c r="AG12">
-        <v>-231.3999999999999</v>
+        <v>-1069.4</v>
       </c>
       <c r="AH12">
-        <v>0.6277356902356902</v>
+        <v>0.6623202747540601</v>
       </c>
       <c r="AI12">
-        <v>0.379830648755332</v>
+        <v>0.3780945734888512</v>
       </c>
       <c r="AJ12">
-        <v>-0.4859302813943717</v>
+        <v>2.185571224197834</v>
       </c>
       <c r="AK12">
-        <v>-0.1347856477166821</v>
+        <v>-1.333250218177284</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.08019999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="E13">
-        <v>0.239</v>
+        <v>0.233</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1951,28 +1951,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>79.90000000000001</v>
+        <v>101.9</v>
       </c>
       <c r="L13">
-        <v>0.2848484848484849</v>
+        <v>0.2707945787935158</v>
       </c>
       <c r="M13">
-        <v>15.6</v>
+        <v>30.2</v>
       </c>
       <c r="N13">
-        <v>0.08719955282280603</v>
+        <v>0.1073968705547653</v>
       </c>
       <c r="O13">
-        <v>0.195244055068836</v>
+        <v>0.296368989205103</v>
       </c>
       <c r="P13">
-        <v>15.6</v>
+        <v>30.2</v>
       </c>
       <c r="Q13">
-        <v>0.08719955282280603</v>
+        <v>0.1073968705547653</v>
       </c>
       <c r="R13">
-        <v>0.195244055068836</v>
+        <v>0.296368989205103</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1981,182 +1981,60 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>673.4</v>
+        <v>733.1</v>
       </c>
       <c r="V13">
-        <v>3.76411403018446</v>
+        <v>2.607041251778094</v>
       </c>
       <c r="W13">
-        <v>0.1166423357664234</v>
+        <v>0.1477239779646274</v>
       </c>
       <c r="X13">
-        <v>0.2273221994016509</v>
+        <v>0.3096592631920821</v>
       </c>
       <c r="Y13">
-        <v>-0.1106798636352275</v>
+        <v>-0.1619352852274547</v>
       </c>
       <c r="Z13">
-        <v>0.3609574057392871</v>
+        <v>0.513509825327511</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.1059645654319197</v>
+        <v>0.1719714665178017</v>
       </c>
       <c r="AC13">
-        <v>-0.1059645654319197</v>
+        <v>-0.1719714665178017</v>
       </c>
       <c r="AD13">
-        <v>716.4</v>
+        <v>1031</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>716.4</v>
+        <v>1031</v>
       </c>
       <c r="AG13">
-        <v>43</v>
+        <v>297.9</v>
       </c>
       <c r="AH13">
-        <v>0.8001787110465766</v>
+        <v>0.7857033988721231</v>
       </c>
       <c r="AI13">
-        <v>0.5094581140662779</v>
+        <v>0.582617540687161</v>
       </c>
       <c r="AJ13">
-        <v>0.1937809824245156</v>
+        <v>0.5144189259195303</v>
       </c>
       <c r="AK13">
-        <v>0.05867903930131005</v>
+        <v>0.2874095513748191</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Access Bank Plc (NGSE:ACCESS)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.163</v>
-      </c>
-      <c r="E14">
-        <v>0.117</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>302.1</v>
-      </c>
-      <c r="L14">
-        <v>0.2415833666533387</v>
-      </c>
-      <c r="M14">
-        <v>23</v>
-      </c>
-      <c r="N14">
-        <v>0.02929563112979238</v>
-      </c>
-      <c r="O14">
-        <v>0.07613373055279708</v>
-      </c>
-      <c r="P14">
-        <v>23</v>
-      </c>
-      <c r="Q14">
-        <v>0.02929563112979238</v>
-      </c>
-      <c r="R14">
-        <v>0.07613373055279708</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>3057</v>
-      </c>
-      <c r="V14">
-        <v>3.893771494077188</v>
-      </c>
-      <c r="W14">
-        <v>0.1722152548170106</v>
-      </c>
-      <c r="X14">
-        <v>0.2553825745002617</v>
-      </c>
-      <c r="Y14">
-        <v>-0.08316731968325114</v>
-      </c>
-      <c r="Z14">
-        <v>0.4873533652909309</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.1070636549662942</v>
-      </c>
-      <c r="AC14">
-        <v>-0.1070636549662942</v>
-      </c>
-      <c r="AD14">
-        <v>3707.9</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>3707.9</v>
-      </c>
-      <c r="AG14">
-        <v>650.9000000000001</v>
-      </c>
-      <c r="AH14">
-        <v>0.8252615179167594</v>
-      </c>
-      <c r="AI14">
-        <v>0.6552565076784421</v>
-      </c>
-      <c r="AJ14">
-        <v>0.4532729805013928</v>
-      </c>
-      <c r="AK14">
-        <v>0.2501825729330823</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.12</v>
+        <v>0.2195</v>
       </c>
       <c r="E2">
-        <v>0.186</v>
+        <v>0.3485</v>
       </c>
       <c r="F2">
-        <v>0.131</v>
+        <v>0.203</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1963</v>
+        <v>1799.77</v>
       </c>
       <c r="L2">
-        <v>0.3015407302723545</v>
+        <v>0.3828320428826683</v>
       </c>
       <c r="M2">
-        <v>687.65</v>
+        <v>286.351</v>
       </c>
       <c r="N2">
-        <v>0.1342961487383798</v>
+        <v>0.07059413751448364</v>
       </c>
       <c r="O2">
-        <v>0.3503056546102903</v>
+        <v>0.1591042188724115</v>
       </c>
       <c r="P2">
-        <v>681.8200000000001</v>
+        <v>281.038</v>
       </c>
       <c r="Q2">
-        <v>0.1331575658151707</v>
+        <v>0.06928432315164065</v>
       </c>
       <c r="R2">
-        <v>0.3473357106469689</v>
+        <v>0.1561521750001389</v>
       </c>
       <c r="S2">
-        <v>5.830000000000013</v>
+        <v>5.313000000000007</v>
       </c>
       <c r="T2">
-        <v>0.008478150221769815</v>
+        <v>0.01855415207210733</v>
       </c>
       <c r="U2">
-        <v>15258.1</v>
+        <v>9610.41</v>
       </c>
       <c r="V2">
-        <v>2.979864854308258</v>
+        <v>2.369255232601139</v>
       </c>
       <c r="W2">
-        <v>0.1477239779646274</v>
+        <v>0.1458581391393094</v>
       </c>
       <c r="X2">
-        <v>0.2190161294526885</v>
+        <v>0.1904857009267194</v>
       </c>
       <c r="Y2">
-        <v>-0.07129215148806103</v>
+        <v>-0.04462756178740995</v>
       </c>
       <c r="Z2">
-        <v>0.6530104142216017</v>
+        <v>0.5619465641555262</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1433619701322168</v>
+        <v>0.1292670324914273</v>
       </c>
       <c r="AC2">
-        <v>-0.1433619701322168</v>
+        <v>-0.1292670324914273</v>
       </c>
       <c r="AD2">
-        <v>12402.14</v>
+        <v>8826.549999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12402.14</v>
+        <v>8826.549999999999</v>
       </c>
       <c r="AG2">
-        <v>-2855.960000000001</v>
+        <v>-783.8600000000006</v>
       </c>
       <c r="AH2">
-        <v>0.7077820909525673</v>
+        <v>0.6851395459855545</v>
       </c>
       <c r="AI2">
-        <v>0.5255179696133534</v>
+        <v>0.5251694973240396</v>
       </c>
       <c r="AJ2">
-        <v>-1.261221317411812</v>
+        <v>-0.2395338035227539</v>
       </c>
       <c r="AK2">
-        <v>-0.3423698173282794</v>
+        <v>-0.1089202739056005</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.12</v>
+        <v>0.208</v>
       </c>
       <c r="E3">
-        <v>-0.0115</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +731,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.34</v>
+        <v>2.37</v>
       </c>
       <c r="L3">
-        <v>0.1072</v>
+        <v>0.2154545454545455</v>
       </c>
       <c r="M3">
-        <v>1.25</v>
+        <v>0.9710000000000001</v>
       </c>
       <c r="N3">
-        <v>0.05530973451327433</v>
+        <v>0.07412213740458017</v>
       </c>
       <c r="O3">
-        <v>0.9328358208955223</v>
+        <v>0.409704641350211</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>0.768</v>
       </c>
       <c r="Q3">
-        <v>0.05530973451327433</v>
+        <v>0.05862595419847329</v>
       </c>
       <c r="R3">
-        <v>0.9328358208955223</v>
+        <v>0.3240506329113924</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.2030000000000001</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2090628218331617</v>
       </c>
       <c r="U3">
-        <v>23.2</v>
+        <v>7.66</v>
       </c>
       <c r="V3">
-        <v>1.026548672566372</v>
+        <v>0.584732824427481</v>
       </c>
       <c r="W3">
-        <v>0.0943661971830986</v>
+        <v>0.09634146341463415</v>
       </c>
       <c r="X3">
-        <v>0.1296589057927731</v>
+        <v>0.1113730509879824</v>
       </c>
       <c r="Y3">
-        <v>-0.03529270860967446</v>
+        <v>-0.01503158757334823</v>
       </c>
       <c r="Z3">
-        <v>0.485248447204969</v>
+        <v>1.443569553805773</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.122466470514737</v>
+        <v>0.1078873002378022</v>
       </c>
       <c r="AC3">
-        <v>-0.122466470514737</v>
+        <v>-0.1078873002378022</v>
       </c>
       <c r="AD3">
-        <v>6.34</v>
+        <v>3.45</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.34</v>
+        <v>3.45</v>
       </c>
       <c r="AG3">
-        <v>-16.86</v>
+        <v>-4.21</v>
       </c>
       <c r="AH3">
-        <v>0.2190739460953697</v>
+        <v>0.2084592145015106</v>
       </c>
       <c r="AI3">
-        <v>0.2082785808147175</v>
+        <v>0.1880108991825613</v>
       </c>
       <c r="AJ3">
-        <v>-2.937282229965156</v>
+        <v>-0.4735658042744657</v>
       </c>
       <c r="AK3">
-        <v>-2.328729281767955</v>
+        <v>-0.3938260056127221</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Guaranty Trust Holding Company Plc (NGSE:GTCO)</t>
+          <t>Wema Bank PLC (NGSE:WEMABANK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0694</v>
+        <v>0.231</v>
       </c>
       <c r="E4">
-        <v>0.04269999999999999</v>
+        <v>0.461</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,85 +853,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>398.8</v>
+        <v>28.7</v>
       </c>
       <c r="L4">
-        <v>0.4129219300062125</v>
+        <v>0.22562893081761</v>
       </c>
       <c r="M4">
-        <v>227.76</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.2082472341592759</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.5711133400200602</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>226.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.2070037487427997</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.567703109327984</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>1.360000000000014</v>
-      </c>
-      <c r="T4">
-        <v>0.00597119775201973</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2729.4</v>
+        <v>180.3</v>
       </c>
       <c r="V4">
-        <v>2.495565511566243</v>
+        <v>2.225925925925926</v>
       </c>
       <c r="W4">
-        <v>0.1981516446387757</v>
+        <v>0.1648477886272257</v>
       </c>
       <c r="X4">
-        <v>0.1319961023607807</v>
+        <v>0.1235357495368856</v>
       </c>
       <c r="Y4">
-        <v>0.06615554227799506</v>
+        <v>0.04131203909034015</v>
       </c>
       <c r="Z4">
-        <v>2.03540569020021</v>
+        <v>1.647668393782384</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1233800433941056</v>
+        <v>0.1133236985023193</v>
       </c>
       <c r="AC4">
-        <v>-0.1233800433941056</v>
+        <v>-0.1133236985023193</v>
       </c>
       <c r="AD4">
-        <v>354.9</v>
+        <v>44.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>354.9</v>
+        <v>44.3</v>
       </c>
       <c r="AG4">
-        <v>-2374.5</v>
+        <v>-136</v>
       </c>
       <c r="AH4">
-        <v>0.2449951677481707</v>
+        <v>0.3535514764565044</v>
       </c>
       <c r="AI4">
-        <v>0.1494378710682555</v>
+        <v>0.2257900101936799</v>
       </c>
       <c r="AJ4">
-        <v>1.853919425359151</v>
+        <v>2.472727272727273</v>
       </c>
       <c r="AK4">
-        <v>6.698166431593794</v>
+        <v>-8.553459119496852</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Bank of Nigeria Plc (NGSE:UBN)</t>
+          <t>Sterling Financial Holdings Company Plc (NGSE:STERLINGNG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0525</v>
+        <v>0.114</v>
       </c>
       <c r="E5">
-        <v>-0.0406</v>
+        <v>0.161</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
       <c r="L5">
-        <v>0.1147875816993464</v>
+        <v>0.1733167082294264</v>
       </c>
       <c r="M5">
-        <v>16.9</v>
+        <v>5.53</v>
       </c>
       <c r="N5">
-        <v>0.04043062200956937</v>
+        <v>0.03981281497480202</v>
       </c>
       <c r="O5">
-        <v>0.6014234875444839</v>
+        <v>0.1989208633093525</v>
       </c>
       <c r="P5">
-        <v>16.9</v>
+        <v>5.53</v>
       </c>
       <c r="Q5">
-        <v>0.04043062200956937</v>
+        <v>0.03981281497480202</v>
       </c>
       <c r="R5">
-        <v>0.6014234875444839</v>
+        <v>0.1989208633093525</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>904.4</v>
+        <v>271.3</v>
       </c>
       <c r="V5">
-        <v>2.163636363636364</v>
+        <v>1.953203743700504</v>
       </c>
       <c r="W5">
-        <v>0.04463860206513106</v>
+        <v>0.07988505747126437</v>
       </c>
       <c r="X5">
-        <v>0.1669024194537139</v>
+        <v>0.2037131109824006</v>
       </c>
       <c r="Y5">
-        <v>-0.1222638173885828</v>
+        <v>-0.1238280535111363</v>
       </c>
       <c r="Z5">
-        <v>0.8242424242424243</v>
+        <v>0.7264492753623186</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1321993729804838</v>
+        <v>0.1265770529720629</v>
       </c>
       <c r="AC5">
-        <v>-0.1321993729804838</v>
+        <v>-0.1265770529720629</v>
       </c>
       <c r="AD5">
-        <v>410.1</v>
+        <v>335.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>410.1</v>
+        <v>335.6</v>
       </c>
       <c r="AG5">
-        <v>-494.3</v>
+        <v>64.30000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.4952300446805942</v>
+        <v>0.7072708113804005</v>
       </c>
       <c r="AI5">
-        <v>0.3960788101216921</v>
+        <v>0.6122970260901296</v>
       </c>
       <c r="AJ5">
-        <v>6.478374836173004</v>
+        <v>0.3164370078740158</v>
       </c>
       <c r="AK5">
-        <v>-3.773282442748091</v>
+        <v>0.2322976878612717</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wema Bank PLC (NGSE:WEMABANK)</t>
+          <t>Access Holdings Plc (NGSE:ACCESSCORP)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1079,10 +1076,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.186</v>
+        <v>0.315</v>
       </c>
       <c r="E6">
-        <v>0.31</v>
+        <v>0.323</v>
+      </c>
+      <c r="F6">
+        <v>0.255</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,85 +1097,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>25.2</v>
+        <v>343</v>
       </c>
       <c r="L6">
-        <v>0.1575</v>
+        <v>0.2806644300793716</v>
       </c>
       <c r="M6">
-        <v>7.14</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="N6">
-        <v>0.06380697050938337</v>
+        <v>0.07548920943754893</v>
       </c>
       <c r="O6">
-        <v>0.2833333333333333</v>
+        <v>0.1968221574344023</v>
       </c>
       <c r="P6">
-        <v>7.14</v>
+        <v>62.4</v>
       </c>
       <c r="Q6">
-        <v>0.06380697050938337</v>
+        <v>0.06977524320697753</v>
       </c>
       <c r="R6">
-        <v>0.2833333333333333</v>
+        <v>0.1819241982507289</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5.110000000000007</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.07569249000148136</v>
       </c>
       <c r="U6">
-        <v>247.2</v>
+        <v>2470</v>
       </c>
       <c r="V6">
-        <v>2.20911528150134</v>
+        <v>2.761936710276194</v>
       </c>
       <c r="W6">
-        <v>0.1620578778135048</v>
+        <v>0.1458581391393094</v>
       </c>
       <c r="X6">
-        <v>0.1861503319588135</v>
+        <v>0.2505904905380039</v>
       </c>
       <c r="Y6">
-        <v>-0.02409245414530869</v>
+        <v>-0.1047323513986944</v>
       </c>
       <c r="Z6">
-        <v>1.773835920177383</v>
+        <v>0.3772728675948507</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1349482977027426</v>
+        <v>0.129235469675727</v>
       </c>
       <c r="AC6">
-        <v>-0.1349482977027426</v>
+        <v>-0.129235469675727</v>
       </c>
       <c r="AD6">
-        <v>150.3</v>
+        <v>3138.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>150.3</v>
+        <v>3138.1</v>
       </c>
       <c r="AG6">
-        <v>-96.89999999999998</v>
+        <v>668.0999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.5732265446224256</v>
+        <v>0.7782214066064875</v>
       </c>
       <c r="AI6">
-        <v>0.4633168927250309</v>
+        <v>0.5988969044620024</v>
       </c>
       <c r="AJ6">
-        <v>-6.459999999999987</v>
+        <v>0.4276113671274961</v>
       </c>
       <c r="AK6">
-        <v>-1.255181347150258</v>
+        <v>0.2412087515344068</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unity Bank Plc (NGSE:UNITYBNK)</t>
+          <t>United Bank for Africa Plc (NGSE:UBA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1201,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0277</v>
+        <v>0.28</v>
       </c>
       <c r="E7">
-        <v>0.22</v>
+        <v>0.461</v>
+      </c>
+      <c r="F7">
+        <v>0.203</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,82 +1222,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>7.56</v>
+        <v>635</v>
       </c>
       <c r="L7">
-        <v>0.1067796610169491</v>
+        <v>0.4844000305133877</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>42.1</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.04265883068193333</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.06629921259842519</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>42.1</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.04265883068193333</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.06629921259842519</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>18.1</v>
+        <v>2030.7</v>
       </c>
       <c r="V7">
-        <v>1.265734265734266</v>
+        <v>2.057655284223326</v>
       </c>
       <c r="W7">
-        <v>-0.01103810775295664</v>
+        <v>0.3532684283727399</v>
       </c>
       <c r="X7">
-        <v>3.842017329789793</v>
+        <v>0.1362074326874438</v>
       </c>
       <c r="Y7">
-        <v>-3.853055437542749</v>
+        <v>0.2170609956852961</v>
       </c>
       <c r="Z7">
-        <v>0.1588868940754039</v>
+        <v>1.800439500068671</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.141557174994369</v>
+        <v>0.1292670324914273</v>
       </c>
       <c r="AC7">
-        <v>-0.141557174994369</v>
+        <v>-0.1292670324914273</v>
       </c>
       <c r="AD7">
-        <v>1002.6</v>
+        <v>831.3</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1002.6</v>
+        <v>831.3</v>
       </c>
       <c r="AG7">
-        <v>984.5</v>
+        <v>-1199.4</v>
       </c>
       <c r="AH7">
-        <v>0.9859376536532599</v>
+        <v>0.4572104278957211</v>
       </c>
       <c r="AI7">
-        <v>2.743091655266758</v>
+        <v>0.2673420164013507</v>
       </c>
       <c r="AJ7">
-        <v>0.98568281938326</v>
+        <v>5.644235294117644</v>
       </c>
       <c r="AK7">
-        <v>2.833909038572251</v>
+        <v>-1.111790878754172</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1317,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sterling Bank Plc (NGSE:STERLNBANK)</t>
+          <t>FCMB Group Plc (NGSE:FCMB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,10 +1326,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.124</v>
+        <v>0.158</v>
       </c>
       <c r="E8">
-        <v>0.258</v>
+        <v>0.318</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1338,28 +1344,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>40.4</v>
+        <v>73.3</v>
       </c>
       <c r="L8">
-        <v>0.1711139347734011</v>
+        <v>0.2875637504903883</v>
       </c>
       <c r="M8">
-        <v>6.66</v>
+        <v>6.34</v>
       </c>
       <c r="N8">
-        <v>0.074</v>
+        <v>0.03844754396604002</v>
       </c>
       <c r="O8">
-        <v>0.1648514851485149</v>
+        <v>0.08649386084583902</v>
       </c>
       <c r="P8">
-        <v>6.66</v>
+        <v>6.34</v>
       </c>
       <c r="Q8">
-        <v>0.074</v>
+        <v>0.03844754396604002</v>
       </c>
       <c r="R8">
-        <v>0.1648514851485149</v>
+        <v>0.08649386084583902</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1368,55 +1374,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>515.8</v>
+        <v>449.8</v>
       </c>
       <c r="V8">
-        <v>5.731111111111111</v>
+        <v>2.727713765918739</v>
       </c>
       <c r="W8">
-        <v>0.1203097081596188</v>
+        <v>0.1206584362139918</v>
       </c>
       <c r="X8">
-        <v>0.3442860847273604</v>
+        <v>0.2746165651059547</v>
       </c>
       <c r="Y8">
-        <v>-0.2239763765677416</v>
+        <v>-0.1539581288919629</v>
       </c>
       <c r="Z8">
-        <v>0.8217890706578487</v>
+        <v>0.2923500401422182</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1433619701322168</v>
+        <v>0.1301536814395816</v>
       </c>
       <c r="AC8">
-        <v>-0.1433619701322168</v>
+        <v>-0.1301536814395816</v>
       </c>
       <c r="AD8">
-        <v>388.6</v>
+        <v>671</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>388.6</v>
+        <v>671</v>
       </c>
       <c r="AG8">
-        <v>-127.1999999999999</v>
+        <v>221.2</v>
       </c>
       <c r="AH8">
-        <v>0.8119515252820727</v>
+        <v>0.8027275989950952</v>
       </c>
       <c r="AI8">
-        <v>0.5275590551181103</v>
+        <v>0.5835797530005219</v>
       </c>
       <c r="AJ8">
-        <v>3.419354838709682</v>
+        <v>0.5729085729085729</v>
       </c>
       <c r="AK8">
-        <v>-0.5760869565217387</v>
+        <v>0.316</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1433,7 +1439,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Access Holdings Plc (NGSE:ACCESSCORP)</t>
+          <t>Unity Bank Plc (NGSE:UNITYBNK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1441,104 +1447,80 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.172</v>
-      </c>
-      <c r="E9">
-        <v>0.186</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
       <c r="K9">
-        <v>399.2</v>
-      </c>
-      <c r="L9">
-        <v>0.2674169346195069</v>
+        <v>-62.8</v>
       </c>
       <c r="M9">
-        <v>83.97</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.1278860798050563</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.2103456913827655</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>79.5</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.1210782820590923</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.1991482965931864</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>4.469999999999999</v>
-      </c>
-      <c r="T9">
-        <v>0.05323329760628795</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2758.6</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="V9">
-        <v>4.201340237587572</v>
+        <v>0.3779342723004695</v>
       </c>
       <c r="W9">
-        <v>0.2091914269244878</v>
+        <v>0.09857165280175796</v>
       </c>
       <c r="X9">
-        <v>0.4123573656721677</v>
+        <v>0.6715891217454184</v>
       </c>
       <c r="Y9">
-        <v>-0.20316593874768</v>
+        <v>-0.5730174689436605</v>
       </c>
       <c r="Z9">
-        <v>0.58994625355675</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1446481283129669</v>
+        <v>0.1349293951836097</v>
       </c>
       <c r="AC9">
-        <v>-0.1446481283129669</v>
+        <v>-0.1349293951836097</v>
       </c>
       <c r="AD9">
-        <v>3675.8</v>
+        <v>283.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3675.8</v>
+        <v>283.8</v>
       </c>
       <c r="AG9">
-        <v>917.2000000000003</v>
+        <v>275.75</v>
       </c>
       <c r="AH9">
-        <v>0.8484442803065275</v>
+        <v>0.9301868239921337</v>
       </c>
       <c r="AI9">
-        <v>0.6055184910633391</v>
+        <v>7.077306733167078</v>
       </c>
       <c r="AJ9">
-        <v>0.58279323929343</v>
+        <v>0.9282948998485103</v>
       </c>
       <c r="AK9">
-        <v>0.2769407288867418</v>
+        <v>8.603744149765987</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1555,7 +1537,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FCMB Group Plc (NGSE:FCMB)</t>
+          <t>Fidelity Bank Plc (NGSE:FIDELITYBK)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1564,10 +1546,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.14</v>
+        <v>0.248</v>
       </c>
       <c r="E10">
-        <v>0.341</v>
+        <v>0.374</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1582,28 +1564,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>68.5</v>
+        <v>132.6</v>
       </c>
       <c r="L10">
-        <v>0.2065119083509195</v>
+        <v>0.3679245283018868</v>
       </c>
       <c r="M10">
-        <v>9.17</v>
+        <v>27.2</v>
       </c>
       <c r="N10">
-        <v>0.05387779083431258</v>
+        <v>0.06961863322242129</v>
       </c>
       <c r="O10">
-        <v>0.1338686131386861</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="P10">
-        <v>9.17</v>
+        <v>27.2</v>
       </c>
       <c r="Q10">
-        <v>0.05387779083431258</v>
+        <v>0.06961863322242129</v>
       </c>
       <c r="R10">
-        <v>0.1338686131386861</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1612,55 +1594,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>703.1</v>
+        <v>728.7</v>
       </c>
       <c r="V10">
-        <v>4.131022326674501</v>
+        <v>1.865113898131559</v>
       </c>
       <c r="W10">
-        <v>0.1191926222376892</v>
+        <v>0.1795288383428107</v>
       </c>
       <c r="X10">
-        <v>0.4320917787956251</v>
+        <v>0.1705047682052405</v>
       </c>
       <c r="Y10">
-        <v>-0.3128991565579359</v>
+        <v>0.0090240701375702</v>
       </c>
       <c r="Z10">
-        <v>0.845095541401274</v>
+        <v>0.3477086348287506</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.1449326310820667</v>
+        <v>0.1397552673050704</v>
       </c>
       <c r="AC10">
-        <v>-0.1449326310820667</v>
+        <v>-0.1397552673050704</v>
       </c>
       <c r="AD10">
-        <v>1016</v>
+        <v>641.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1016</v>
+        <v>641.5</v>
       </c>
       <c r="AG10">
-        <v>312.9</v>
+        <v>-87.20000000000005</v>
       </c>
       <c r="AH10">
-        <v>0.8565166076546956</v>
+        <v>0.6214880837047083</v>
       </c>
       <c r="AI10">
-        <v>0.624923114774265</v>
+        <v>0.5493235143003939</v>
       </c>
       <c r="AJ10">
-        <v>0.647691989236183</v>
+        <v>-0.2873146622734763</v>
       </c>
       <c r="AK10">
-        <v>0.3391134713341281</v>
+        <v>-0.1985880209519473</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1686,13 +1668,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0989</v>
+        <v>0.173</v>
       </c>
       <c r="E11">
-        <v>0.096</v>
+        <v>0.208</v>
       </c>
       <c r="F11">
-        <v>0.131</v>
+        <v>0.137</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1707,28 +1689,28 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>597.5</v>
+        <v>619.8</v>
       </c>
       <c r="L11">
-        <v>0.41045545098578</v>
+        <v>0.494140157856972</v>
       </c>
       <c r="M11">
-        <v>225.4</v>
+        <v>136.7</v>
       </c>
       <c r="N11">
-        <v>0.1340230705196813</v>
+        <v>0.1001318488133607</v>
       </c>
       <c r="O11">
-        <v>0.3772384937238494</v>
+        <v>0.2205550177476605</v>
       </c>
       <c r="P11">
-        <v>225.4</v>
+        <v>136.7</v>
       </c>
       <c r="Q11">
-        <v>0.1340230705196813</v>
+        <v>0.1001318488133607</v>
       </c>
       <c r="R11">
-        <v>0.3772384937238494</v>
+        <v>0.2205550177476605</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1737,304 +1719,60 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>4418</v>
+        <v>3463.9</v>
       </c>
       <c r="V11">
-        <v>2.626947318349388</v>
+        <v>2.53728391444477</v>
       </c>
       <c r="W11">
-        <v>0.206447377513648</v>
+        <v>0.2047977795400475</v>
       </c>
       <c r="X11">
-        <v>0.216804725042037</v>
+        <v>0.1904857009267194</v>
       </c>
       <c r="Y11">
-        <v>-0.01035734752838902</v>
+        <v>0.01431207861332817</v>
       </c>
       <c r="Z11">
-        <v>0.4767784619415695</v>
+        <v>0.6827608731152358</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1626345597320497</v>
+        <v>0.1433775324542318</v>
       </c>
       <c r="AC11">
-        <v>-0.1626345597320497</v>
+        <v>-0.1433775324542318</v>
       </c>
       <c r="AD11">
-        <v>3228.7</v>
+        <v>2877.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>3228.7</v>
+        <v>2877.5</v>
       </c>
       <c r="AG11">
-        <v>-1189.3</v>
+        <v>-586.4000000000001</v>
       </c>
       <c r="AH11">
-        <v>0.6575094185928113</v>
+        <v>0.6782237725976383</v>
       </c>
       <c r="AI11">
-        <v>0.5159810784031706</v>
+        <v>0.5391201708697119</v>
       </c>
       <c r="AJ11">
-        <v>-2.414822335025382</v>
+        <v>-0.7529532614278378</v>
       </c>
       <c r="AK11">
-        <v>-0.6465695335435471</v>
+        <v>-0.3129970643181212</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>United Bank for Africa Plc (NGSE:UBA)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.114</v>
-      </c>
-      <c r="E12">
-        <v>0.0953</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>294.5</v>
-      </c>
-      <c r="L12">
-        <v>0.2531373560254426</v>
-      </c>
-      <c r="M12">
-        <v>79.2</v>
-      </c>
-      <c r="N12">
-        <v>0.1365281847957249</v>
-      </c>
-      <c r="O12">
-        <v>0.2689303904923599</v>
-      </c>
-      <c r="P12">
-        <v>79.2</v>
-      </c>
-      <c r="Q12">
-        <v>0.1365281847957249</v>
-      </c>
-      <c r="R12">
-        <v>0.2689303904923599</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>2207.2</v>
-      </c>
-      <c r="V12">
-        <v>3.804861230822271</v>
-      </c>
-      <c r="W12">
-        <v>0.1573856348867037</v>
-      </c>
-      <c r="X12">
-        <v>0.2190161294526885</v>
-      </c>
-      <c r="Y12">
-        <v>-0.06163049456598477</v>
-      </c>
-      <c r="Z12">
-        <v>0.7094767654592024</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.1629849546214148</v>
-      </c>
-      <c r="AC12">
-        <v>-0.1629849546214148</v>
-      </c>
-      <c r="AD12">
-        <v>1137.8</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>1137.8</v>
-      </c>
-      <c r="AG12">
-        <v>-1069.4</v>
-      </c>
-      <c r="AH12">
-        <v>0.6623202747540601</v>
-      </c>
-      <c r="AI12">
-        <v>0.3780945734888512</v>
-      </c>
-      <c r="AJ12">
-        <v>2.185571224197834</v>
-      </c>
-      <c r="AK12">
-        <v>-1.333250218177284</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Fidelity Bank Plc (NGSE:FIDELITYBK)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.143</v>
-      </c>
-      <c r="E13">
-        <v>0.233</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>101.9</v>
-      </c>
-      <c r="L13">
-        <v>0.2707945787935158</v>
-      </c>
-      <c r="M13">
-        <v>30.2</v>
-      </c>
-      <c r="N13">
-        <v>0.1073968705547653</v>
-      </c>
-      <c r="O13">
-        <v>0.296368989205103</v>
-      </c>
-      <c r="P13">
-        <v>30.2</v>
-      </c>
-      <c r="Q13">
-        <v>0.1073968705547653</v>
-      </c>
-      <c r="R13">
-        <v>0.296368989205103</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>733.1</v>
-      </c>
-      <c r="V13">
-        <v>2.607041251778094</v>
-      </c>
-      <c r="W13">
-        <v>0.1477239779646274</v>
-      </c>
-      <c r="X13">
-        <v>0.3096592631920821</v>
-      </c>
-      <c r="Y13">
-        <v>-0.1619352852274547</v>
-      </c>
-      <c r="Z13">
-        <v>0.513509825327511</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.1719714665178017</v>
-      </c>
-      <c r="AC13">
-        <v>-0.1719714665178017</v>
-      </c>
-      <c r="AD13">
-        <v>1031</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>1031</v>
-      </c>
-      <c r="AG13">
-        <v>297.9</v>
-      </c>
-      <c r="AH13">
-        <v>0.7857033988721231</v>
-      </c>
-      <c r="AI13">
-        <v>0.582617540687161</v>
-      </c>
-      <c r="AJ13">
-        <v>0.5144189259195303</v>
-      </c>
-      <c r="AK13">
-        <v>0.2874095513748191</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2195</v>
+        <v>0.383</v>
       </c>
       <c r="E2">
-        <v>0.3485</v>
+        <v>0.5195000000000001</v>
       </c>
       <c r="F2">
-        <v>0.203</v>
+        <v>0.111</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1799.77</v>
+        <v>1539.1</v>
       </c>
       <c r="L2">
-        <v>0.3828320428826683</v>
+        <v>0.413914586919105</v>
       </c>
       <c r="M2">
-        <v>286.351</v>
+        <v>153.8</v>
       </c>
       <c r="N2">
-        <v>0.07059413751448364</v>
+        <v>0.05699251463721931</v>
       </c>
       <c r="O2">
-        <v>0.1591042188724115</v>
+        <v>0.09992852966019102</v>
       </c>
       <c r="P2">
-        <v>281.038</v>
+        <v>153.8</v>
       </c>
       <c r="Q2">
-        <v>0.06928432315164065</v>
+        <v>0.05699251463721931</v>
       </c>
       <c r="R2">
-        <v>0.1561521750001389</v>
+        <v>0.09992852966019102</v>
       </c>
       <c r="S2">
-        <v>5.313000000000007</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01855415207210733</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>9610.41</v>
+        <v>7944.2</v>
       </c>
       <c r="V2">
-        <v>2.369255232601139</v>
+        <v>2.943822722893352</v>
       </c>
       <c r="W2">
-        <v>0.1458581391393094</v>
+        <v>0.2340925711284413</v>
       </c>
       <c r="X2">
-        <v>0.1904857009267194</v>
+        <v>0.1658507702366079</v>
       </c>
       <c r="Y2">
-        <v>-0.04462756178740995</v>
+        <v>0.06824180089183338</v>
       </c>
       <c r="Z2">
-        <v>0.5619465641555262</v>
+        <v>0.934060137154915</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1292670324914273</v>
+        <v>0.1344762823190022</v>
       </c>
       <c r="AC2">
-        <v>-0.1292670324914273</v>
+        <v>-0.1344762823190022</v>
       </c>
       <c r="AD2">
-        <v>8826.549999999999</v>
+        <v>4027.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8826.549999999999</v>
+        <v>4027.2</v>
       </c>
       <c r="AG2">
-        <v>-783.8600000000006</v>
+        <v>-3917</v>
       </c>
       <c r="AH2">
-        <v>0.6851395459855545</v>
+        <v>0.598768919682417</v>
       </c>
       <c r="AI2">
-        <v>0.5251694973240396</v>
+        <v>0.3927404647896939</v>
       </c>
       <c r="AJ2">
-        <v>-0.2395338035227539</v>
+        <v>3.214871963230466</v>
       </c>
       <c r="AK2">
-        <v>-0.1089202739056005</v>
+        <v>-1.695744404519676</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NPF Microfinance Bank Plc (NGSE:NPFMCRFBK)</t>
+          <t>United Bank for Africa Plc (NGSE:UBA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.208</v>
+        <v>0.414</v>
       </c>
       <c r="E3">
-        <v>0.3779999999999999</v>
+        <v>0.472</v>
+      </c>
+      <c r="F3">
+        <v>0.08500000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2.37</v>
+        <v>397</v>
       </c>
       <c r="L3">
-        <v>0.2154545454545455</v>
+        <v>0.3489496352289707</v>
       </c>
       <c r="M3">
-        <v>0.9710000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="N3">
-        <v>0.07412213740458017</v>
+        <v>0.07619931089318845</v>
       </c>
       <c r="O3">
-        <v>0.409704641350211</v>
+        <v>0.1448362720403023</v>
       </c>
       <c r="P3">
-        <v>0.768</v>
+        <v>57.5</v>
       </c>
       <c r="Q3">
-        <v>0.05862595419847329</v>
+        <v>0.07619931089318845</v>
       </c>
       <c r="R3">
-        <v>0.3240506329113924</v>
+        <v>0.1448362720403023</v>
       </c>
       <c r="S3">
-        <v>0.2030000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.2090628218331617</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>7.66</v>
+        <v>2761.6</v>
       </c>
       <c r="V3">
-        <v>0.584732824427481</v>
+        <v>3.659687251523986</v>
       </c>
       <c r="W3">
-        <v>0.09634146341463415</v>
+        <v>0.1797030599311968</v>
       </c>
       <c r="X3">
-        <v>0.1113730509879824</v>
+        <v>0.138091186188758</v>
       </c>
       <c r="Y3">
-        <v>-0.01503158757334823</v>
+        <v>0.04161187374243883</v>
       </c>
       <c r="Z3">
-        <v>1.443569553805773</v>
+        <v>1.126658744305803</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1078873002378022</v>
+        <v>0.1271013967542108</v>
       </c>
       <c r="AC3">
-        <v>-0.1078873002378022</v>
+        <v>-0.1271013967542108</v>
       </c>
       <c r="AD3">
-        <v>3.45</v>
+        <v>684.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.45</v>
+        <v>684.5</v>
       </c>
       <c r="AG3">
-        <v>-4.21</v>
+        <v>-2077.1</v>
       </c>
       <c r="AH3">
-        <v>0.2084592145015106</v>
+        <v>0.475644500034744</v>
       </c>
       <c r="AI3">
-        <v>0.1880108991825613</v>
+        <v>0.2413866064816448</v>
       </c>
       <c r="AJ3">
-        <v>-0.4735658042744657</v>
+        <v>1.570586011342155</v>
       </c>
       <c r="AK3">
-        <v>-0.3938260056127221</v>
+        <v>-28.03103913630233</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wema Bank PLC (NGSE:WEMABANK)</t>
+          <t>FBN Holdings Plc (NGSE:FBNH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.231</v>
+        <v>0.355</v>
       </c>
       <c r="E4">
-        <v>0.461</v>
+        <v>0.5670000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>28.7</v>
+        <v>361</v>
       </c>
       <c r="L4">
-        <v>0.22562893081761</v>
+        <v>0.3773782145097219</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,55 +883,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>180.3</v>
+        <v>2783.2</v>
       </c>
       <c r="V4">
-        <v>2.225925925925926</v>
+        <v>4.258913542463657</v>
       </c>
       <c r="W4">
-        <v>0.1648477886272257</v>
+        <v>0.2071617123837943</v>
       </c>
       <c r="X4">
-        <v>0.1235357495368856</v>
+        <v>0.1651375631382103</v>
       </c>
       <c r="Y4">
-        <v>0.04131203909034015</v>
+        <v>0.04202414924558406</v>
       </c>
       <c r="Z4">
-        <v>1.647668393782384</v>
+        <v>1.44939393939394</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1133236985023193</v>
+        <v>0.1343377886750028</v>
       </c>
       <c r="AC4">
-        <v>-0.1133236985023193</v>
+        <v>-0.1343377886750028</v>
       </c>
       <c r="AD4">
-        <v>44.3</v>
+        <v>1040.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>44.3</v>
+        <v>1040.1</v>
       </c>
       <c r="AG4">
-        <v>-136</v>
+        <v>-1743.1</v>
       </c>
       <c r="AH4">
-        <v>0.3535514764565044</v>
+        <v>0.6141355692017005</v>
       </c>
       <c r="AI4">
-        <v>0.2257900101936799</v>
+        <v>0.4004234841193455</v>
       </c>
       <c r="AJ4">
-        <v>2.472727272727273</v>
+        <v>1.599761380323054</v>
       </c>
       <c r="AK4">
-        <v>-8.553459119496852</v>
+        <v>9.386645126548204</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sterling Financial Holdings Company Plc (NGSE:STERLINGNG)</t>
+          <t>Fidelity Bank Plc (NGSE:FIDELITYBK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +957,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.114</v>
+        <v>0.411</v>
       </c>
       <c r="E5">
-        <v>0.161</v>
+        <v>0.573</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,28 +975,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>27.8</v>
+        <v>139.4</v>
       </c>
       <c r="L5">
-        <v>0.1733167082294264</v>
+        <v>0.3861495844875347</v>
       </c>
       <c r="M5">
-        <v>5.53</v>
+        <v>11.5</v>
       </c>
       <c r="N5">
-        <v>0.03981281497480202</v>
+        <v>0.03164556962025317</v>
       </c>
       <c r="O5">
-        <v>0.1989208633093525</v>
+        <v>0.08249641319942611</v>
       </c>
       <c r="P5">
-        <v>5.53</v>
+        <v>11.5</v>
       </c>
       <c r="Q5">
-        <v>0.03981281497480202</v>
+        <v>0.03164556962025317</v>
       </c>
       <c r="R5">
-        <v>0.1989208633093525</v>
+        <v>0.08249641319942611</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1002,55 +1005,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>271.3</v>
+        <v>695.2</v>
       </c>
       <c r="V5">
-        <v>1.953203743700504</v>
+        <v>1.91304347826087</v>
       </c>
       <c r="W5">
-        <v>0.07988505747126437</v>
+        <v>0.2648679460383812</v>
       </c>
       <c r="X5">
-        <v>0.2037131109824006</v>
+        <v>0.1665639773350055</v>
       </c>
       <c r="Y5">
-        <v>-0.1238280535111363</v>
+        <v>0.09830396870337571</v>
       </c>
       <c r="Z5">
-        <v>0.7264492753623186</v>
+        <v>0.8221361876565705</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1265770529720629</v>
+        <v>0.1346147759630016</v>
       </c>
       <c r="AC5">
-        <v>-0.1265770529720629</v>
+        <v>-0.1346147759630016</v>
       </c>
       <c r="AD5">
-        <v>335.6</v>
+        <v>591.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>335.6</v>
+        <v>591.5</v>
       </c>
       <c r="AG5">
-        <v>64.30000000000001</v>
+        <v>-103.7</v>
       </c>
       <c r="AH5">
-        <v>0.7072708113804005</v>
+        <v>0.6194365902188711</v>
       </c>
       <c r="AI5">
-        <v>0.6122970260901296</v>
+        <v>0.5888501742160279</v>
       </c>
       <c r="AJ5">
-        <v>0.3164370078740158</v>
+        <v>-0.3993068925683484</v>
       </c>
       <c r="AK5">
-        <v>0.2322976878612717</v>
+        <v>-0.3352731975428389</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1067,7 +1070,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Access Holdings Plc (NGSE:ACCESSCORP)</t>
+          <t>Zenith Bank Plc (NGSE:ZENITHBANK)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1079,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.315</v>
+        <v>0.351</v>
       </c>
       <c r="E6">
-        <v>0.323</v>
+        <v>0.398</v>
       </c>
       <c r="F6">
-        <v>0.255</v>
+        <v>0.137</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,682 +1100,90 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>343</v>
+        <v>641.7</v>
       </c>
       <c r="L6">
-        <v>0.2806644300793716</v>
+        <v>0.508035784973478</v>
       </c>
       <c r="M6">
-        <v>67.51000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="N6">
-        <v>0.07548920943754893</v>
+        <v>0.09146801855247545</v>
       </c>
       <c r="O6">
-        <v>0.1968221574344023</v>
+        <v>0.132148979273804</v>
       </c>
       <c r="P6">
-        <v>62.4</v>
+        <v>84.8</v>
       </c>
       <c r="Q6">
-        <v>0.06977524320697753</v>
+        <v>0.09146801855247545</v>
       </c>
       <c r="R6">
-        <v>0.1819241982507289</v>
+        <v>0.132148979273804</v>
       </c>
       <c r="S6">
-        <v>5.110000000000007</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.07569249000148136</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>2470</v>
+        <v>1704.2</v>
       </c>
       <c r="V6">
-        <v>2.761936710276194</v>
+        <v>1.838205155862366</v>
       </c>
       <c r="W6">
-        <v>0.1458581391393094</v>
+        <v>0.2610234298730882</v>
       </c>
       <c r="X6">
-        <v>0.2505904905380039</v>
+        <v>0.1751765741414752</v>
       </c>
       <c r="Y6">
-        <v>-0.1047323513986944</v>
+        <v>0.08584685573161299</v>
       </c>
       <c r="Z6">
-        <v>0.3772728675948507</v>
+        <v>0.6747329059829061</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.129235469675727</v>
+        <v>0.1361378899982333</v>
       </c>
       <c r="AC6">
-        <v>-0.129235469675727</v>
+        <v>-0.1361378899982333</v>
       </c>
       <c r="AD6">
-        <v>3138.1</v>
+        <v>1711.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3138.1</v>
+        <v>1711.1</v>
       </c>
       <c r="AG6">
-        <v>668.0999999999999</v>
+        <v>6.899999999999864</v>
       </c>
       <c r="AH6">
-        <v>0.7782214066064875</v>
+        <v>0.6485861572284133</v>
       </c>
       <c r="AI6">
-        <v>0.5988969044620024</v>
+        <v>0.4483544701813227</v>
       </c>
       <c r="AJ6">
-        <v>0.4276113671274961</v>
+        <v>0.007387580299785722</v>
       </c>
       <c r="AK6">
-        <v>0.2412087515344068</v>
+        <v>0.003266736104535491</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>United Bank for Africa Plc (NGSE:UBA)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.28</v>
-      </c>
-      <c r="E7">
-        <v>0.461</v>
-      </c>
-      <c r="F7">
-        <v>0.203</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>635</v>
-      </c>
-      <c r="L7">
-        <v>0.4844000305133877</v>
-      </c>
-      <c r="M7">
-        <v>42.1</v>
-      </c>
-      <c r="N7">
-        <v>0.04265883068193333</v>
-      </c>
-      <c r="O7">
-        <v>0.06629921259842519</v>
-      </c>
-      <c r="P7">
-        <v>42.1</v>
-      </c>
-      <c r="Q7">
-        <v>0.04265883068193333</v>
-      </c>
-      <c r="R7">
-        <v>0.06629921259842519</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>2030.7</v>
-      </c>
-      <c r="V7">
-        <v>2.057655284223326</v>
-      </c>
-      <c r="W7">
-        <v>0.3532684283727399</v>
-      </c>
-      <c r="X7">
-        <v>0.1362074326874438</v>
-      </c>
-      <c r="Y7">
-        <v>0.2170609956852961</v>
-      </c>
-      <c r="Z7">
-        <v>1.800439500068671</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.1292670324914273</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1292670324914273</v>
-      </c>
-      <c r="AD7">
-        <v>831.3</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>831.3</v>
-      </c>
-      <c r="AG7">
-        <v>-1199.4</v>
-      </c>
-      <c r="AH7">
-        <v>0.4572104278957211</v>
-      </c>
-      <c r="AI7">
-        <v>0.2673420164013507</v>
-      </c>
-      <c r="AJ7">
-        <v>5.644235294117644</v>
-      </c>
-      <c r="AK7">
-        <v>-1.111790878754172</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FCMB Group Plc (NGSE:FCMB)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.158</v>
-      </c>
-      <c r="E8">
-        <v>0.318</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>73.3</v>
-      </c>
-      <c r="L8">
-        <v>0.2875637504903883</v>
-      </c>
-      <c r="M8">
-        <v>6.34</v>
-      </c>
-      <c r="N8">
-        <v>0.03844754396604002</v>
-      </c>
-      <c r="O8">
-        <v>0.08649386084583902</v>
-      </c>
-      <c r="P8">
-        <v>6.34</v>
-      </c>
-      <c r="Q8">
-        <v>0.03844754396604002</v>
-      </c>
-      <c r="R8">
-        <v>0.08649386084583902</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>449.8</v>
-      </c>
-      <c r="V8">
-        <v>2.727713765918739</v>
-      </c>
-      <c r="W8">
-        <v>0.1206584362139918</v>
-      </c>
-      <c r="X8">
-        <v>0.2746165651059547</v>
-      </c>
-      <c r="Y8">
-        <v>-0.1539581288919629</v>
-      </c>
-      <c r="Z8">
-        <v>0.2923500401422182</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.1301536814395816</v>
-      </c>
-      <c r="AC8">
-        <v>-0.1301536814395816</v>
-      </c>
-      <c r="AD8">
-        <v>671</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>671</v>
-      </c>
-      <c r="AG8">
-        <v>221.2</v>
-      </c>
-      <c r="AH8">
-        <v>0.8027275989950952</v>
-      </c>
-      <c r="AI8">
-        <v>0.5835797530005219</v>
-      </c>
-      <c r="AJ8">
-        <v>0.5729085729085729</v>
-      </c>
-      <c r="AK8">
-        <v>0.316</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Unity Bank Plc (NGSE:UNITYBNK)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="K9">
-        <v>-62.8</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="V9">
-        <v>0.3779342723004695</v>
-      </c>
-      <c r="W9">
-        <v>0.09857165280175796</v>
-      </c>
-      <c r="X9">
-        <v>0.6715891217454184</v>
-      </c>
-      <c r="Y9">
-        <v>-0.5730174689436605</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.1349293951836097</v>
-      </c>
-      <c r="AC9">
-        <v>-0.1349293951836097</v>
-      </c>
-      <c r="AD9">
-        <v>283.8</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>283.8</v>
-      </c>
-      <c r="AG9">
-        <v>275.75</v>
-      </c>
-      <c r="AH9">
-        <v>0.9301868239921337</v>
-      </c>
-      <c r="AI9">
-        <v>7.077306733167078</v>
-      </c>
-      <c r="AJ9">
-        <v>0.9282948998485103</v>
-      </c>
-      <c r="AK9">
-        <v>8.603744149765987</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Fidelity Bank Plc (NGSE:FIDELITYBK)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.248</v>
-      </c>
-      <c r="E10">
-        <v>0.374</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>132.6</v>
-      </c>
-      <c r="L10">
-        <v>0.3679245283018868</v>
-      </c>
-      <c r="M10">
-        <v>27.2</v>
-      </c>
-      <c r="N10">
-        <v>0.06961863322242129</v>
-      </c>
-      <c r="O10">
-        <v>0.2051282051282051</v>
-      </c>
-      <c r="P10">
-        <v>27.2</v>
-      </c>
-      <c r="Q10">
-        <v>0.06961863322242129</v>
-      </c>
-      <c r="R10">
-        <v>0.2051282051282051</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>728.7</v>
-      </c>
-      <c r="V10">
-        <v>1.865113898131559</v>
-      </c>
-      <c r="W10">
-        <v>0.1795288383428107</v>
-      </c>
-      <c r="X10">
-        <v>0.1705047682052405</v>
-      </c>
-      <c r="Y10">
-        <v>0.0090240701375702</v>
-      </c>
-      <c r="Z10">
-        <v>0.3477086348287506</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.1397552673050704</v>
-      </c>
-      <c r="AC10">
-        <v>-0.1397552673050704</v>
-      </c>
-      <c r="AD10">
-        <v>641.5</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>641.5</v>
-      </c>
-      <c r="AG10">
-        <v>-87.20000000000005</v>
-      </c>
-      <c r="AH10">
-        <v>0.6214880837047083</v>
-      </c>
-      <c r="AI10">
-        <v>0.5493235143003939</v>
-      </c>
-      <c r="AJ10">
-        <v>-0.2873146622734763</v>
-      </c>
-      <c r="AK10">
-        <v>-0.1985880209519473</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Zenith Bank Plc (NGSE:ZENITHBANK)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.173</v>
-      </c>
-      <c r="E11">
-        <v>0.208</v>
-      </c>
-      <c r="F11">
-        <v>0.137</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>619.8</v>
-      </c>
-      <c r="L11">
-        <v>0.494140157856972</v>
-      </c>
-      <c r="M11">
-        <v>136.7</v>
-      </c>
-      <c r="N11">
-        <v>0.1001318488133607</v>
-      </c>
-      <c r="O11">
-        <v>0.2205550177476605</v>
-      </c>
-      <c r="P11">
-        <v>136.7</v>
-      </c>
-      <c r="Q11">
-        <v>0.1001318488133607</v>
-      </c>
-      <c r="R11">
-        <v>0.2205550177476605</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>3463.9</v>
-      </c>
-      <c r="V11">
-        <v>2.53728391444477</v>
-      </c>
-      <c r="W11">
-        <v>0.2047977795400475</v>
-      </c>
-      <c r="X11">
-        <v>0.1904857009267194</v>
-      </c>
-      <c r="Y11">
-        <v>0.01431207861332817</v>
-      </c>
-      <c r="Z11">
-        <v>0.6827608731152358</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.1433775324542318</v>
-      </c>
-      <c r="AC11">
-        <v>-0.1433775324542318</v>
-      </c>
-      <c r="AD11">
-        <v>2877.5</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>2877.5</v>
-      </c>
-      <c r="AG11">
-        <v>-586.4000000000001</v>
-      </c>
-      <c r="AH11">
-        <v>0.6782237725976383</v>
-      </c>
-      <c r="AI11">
-        <v>0.5391201708697119</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.7529532614278378</v>
-      </c>
-      <c r="AK11">
-        <v>-0.3129970643181212</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.383</v>
+        <v>0.356</v>
       </c>
       <c r="E2">
-        <v>0.5195000000000001</v>
+        <v>0.508</v>
       </c>
       <c r="F2">
         <v>0.111</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1539.1</v>
+        <v>2160.1</v>
       </c>
       <c r="L2">
-        <v>0.413914586919105</v>
+        <v>0.3925598807836295</v>
       </c>
       <c r="M2">
-        <v>153.8</v>
+        <v>209.572</v>
       </c>
       <c r="N2">
-        <v>0.05699251463721931</v>
+        <v>0.05847922538158887</v>
       </c>
       <c r="O2">
-        <v>0.09992852966019102</v>
+        <v>0.09701958242673951</v>
       </c>
       <c r="P2">
-        <v>153.8</v>
+        <v>209.09</v>
       </c>
       <c r="Q2">
-        <v>0.05699251463721931</v>
+        <v>0.05834472751625416</v>
       </c>
       <c r="R2">
-        <v>0.09992852966019102</v>
+        <v>0.09679644460904588</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.4819999999999993</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.00229992556257515</v>
       </c>
       <c r="U2">
-        <v>7944.2</v>
+        <v>12227.2</v>
       </c>
       <c r="V2">
-        <v>2.943822722893352</v>
+        <v>3.41189273655719</v>
       </c>
       <c r="W2">
-        <v>0.2340925711284413</v>
+        <v>0.2224204399342887</v>
       </c>
       <c r="X2">
-        <v>0.1658507702366079</v>
+        <v>0.1658681426497279</v>
       </c>
       <c r="Y2">
-        <v>0.06824180089183338</v>
+        <v>0.05655229728456074</v>
       </c>
       <c r="Z2">
-        <v>0.934060137154915</v>
+        <v>0.7238548764766241</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1344762823190022</v>
+        <v>0.1267618968082745</v>
       </c>
       <c r="AC2">
-        <v>-0.1344762823190022</v>
+        <v>-0.1267618968082745</v>
       </c>
       <c r="AD2">
-        <v>4027.2</v>
+        <v>7082.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4027.2</v>
+        <v>7082.9</v>
       </c>
       <c r="AG2">
-        <v>-3917</v>
+        <v>-5144.300000000001</v>
       </c>
       <c r="AH2">
-        <v>0.598768919682417</v>
+        <v>0.6640260251626573</v>
       </c>
       <c r="AI2">
-        <v>0.3927404647896939</v>
+        <v>0.4453757734292469</v>
       </c>
       <c r="AJ2">
-        <v>3.214871963230466</v>
+        <v>3.296360374215043</v>
       </c>
       <c r="AK2">
-        <v>-1.695744404519676</v>
+        <v>-1.399428726877041</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>United Bank for Africa Plc (NGSE:UBA)</t>
+          <t>Wema Bank PLC (NGSE:WEMABANK)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.414</v>
+        <v>0.357</v>
       </c>
       <c r="E3">
-        <v>0.472</v>
-      </c>
-      <c r="F3">
-        <v>0.08500000000000001</v>
+        <v>0.7090000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +731,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>397</v>
+        <v>41.7</v>
       </c>
       <c r="L3">
-        <v>0.3489496352289707</v>
+        <v>0.3489539748953975</v>
       </c>
       <c r="M3">
-        <v>57.5</v>
+        <v>3.86</v>
       </c>
       <c r="N3">
-        <v>0.07619931089318845</v>
+        <v>0.03048973143759874</v>
       </c>
       <c r="O3">
-        <v>0.1448362720403023</v>
+        <v>0.09256594724220622</v>
       </c>
       <c r="P3">
-        <v>57.5</v>
+        <v>3.86</v>
       </c>
       <c r="Q3">
-        <v>0.07619931089318845</v>
+        <v>0.03048973143759874</v>
       </c>
       <c r="R3">
-        <v>0.1448362720403023</v>
+        <v>0.09256594724220622</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +761,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2761.6</v>
+        <v>128.1</v>
       </c>
       <c r="V3">
-        <v>3.659687251523986</v>
+        <v>1.011848341232227</v>
       </c>
       <c r="W3">
-        <v>0.1797030599311968</v>
+        <v>0.2745227123107308</v>
       </c>
       <c r="X3">
-        <v>0.138091186188758</v>
+        <v>0.1246069830746938</v>
       </c>
       <c r="Y3">
-        <v>0.04161187374243883</v>
+        <v>0.149915729236037</v>
       </c>
       <c r="Z3">
-        <v>1.126658744305803</v>
+        <v>7.515723270440263</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1271013967542108</v>
+        <v>0.1129888369666794</v>
       </c>
       <c r="AC3">
-        <v>-0.1271013967542108</v>
+        <v>-0.1129888369666794</v>
       </c>
       <c r="AD3">
-        <v>684.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>684.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>-2077.1</v>
+        <v>-56.5</v>
       </c>
       <c r="AH3">
-        <v>0.475644500034744</v>
+        <v>0.3612512613521695</v>
       </c>
       <c r="AI3">
-        <v>0.2413866064816448</v>
+        <v>0.3467312348668281</v>
       </c>
       <c r="AJ3">
-        <v>1.570586011342155</v>
+        <v>-0.8059914407988589</v>
       </c>
       <c r="AK3">
-        <v>-28.03103913630233</v>
+        <v>-0.7206632653061223</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FBN Holdings Plc (NGSE:FBNH)</t>
+          <t>Sterling Financial Holdings Company Plc (NGSE:STERLINGNG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.355</v>
+        <v>0.175</v>
       </c>
       <c r="E4">
-        <v>0.5670000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>361</v>
+        <v>19.5</v>
       </c>
       <c r="L4">
-        <v>0.3773782145097219</v>
+        <v>0.1961770623742455</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2783.2</v>
+        <v>275</v>
       </c>
       <c r="V4">
-        <v>4.258913542463657</v>
+        <v>2.629063097514341</v>
       </c>
       <c r="W4">
-        <v>0.2071617123837943</v>
+        <v>0.09176470588235294</v>
       </c>
       <c r="X4">
-        <v>0.1651375631382103</v>
+        <v>0.1650491713679887</v>
       </c>
       <c r="Y4">
-        <v>0.04202414924558406</v>
+        <v>-0.0732844654856358</v>
       </c>
       <c r="Z4">
-        <v>1.44939393939394</v>
+        <v>0.3591040462427746</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1343377886750028</v>
+        <v>0.1204899975690715</v>
       </c>
       <c r="AC4">
-        <v>-0.1343377886750028</v>
+        <v>-0.1204899975690715</v>
       </c>
       <c r="AD4">
-        <v>1040.1</v>
+        <v>166.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1040.1</v>
+        <v>166.2</v>
       </c>
       <c r="AG4">
-        <v>-1743.1</v>
+        <v>-108.8</v>
       </c>
       <c r="AH4">
-        <v>0.6141355692017005</v>
+        <v>0.6137370753323487</v>
       </c>
       <c r="AI4">
-        <v>0.4004234841193455</v>
+        <v>0.5713303540735648</v>
       </c>
       <c r="AJ4">
-        <v>1.599761380323054</v>
+        <v>25.9047619047618</v>
       </c>
       <c r="AK4">
-        <v>9.386645126548204</v>
+        <v>-6.842767295597489</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -948,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fidelity Bank Plc (NGSE:FIDELITYBK)</t>
+          <t>FCMB Group Plc (NGSE:FCMB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -957,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.411</v>
+        <v>0.282</v>
       </c>
       <c r="E5">
-        <v>0.573</v>
+        <v>0.544</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>139.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="L5">
-        <v>0.3861495844875347</v>
+        <v>0.357615894039735</v>
       </c>
       <c r="M5">
-        <v>11.5</v>
+        <v>6.93</v>
       </c>
       <c r="N5">
-        <v>0.03164556962025317</v>
+        <v>0.05736754966887417</v>
       </c>
       <c r="O5">
-        <v>0.08249641319942611</v>
+        <v>0.09166666666666667</v>
       </c>
       <c r="P5">
-        <v>11.5</v>
+        <v>6.93</v>
       </c>
       <c r="Q5">
-        <v>0.03164556962025317</v>
+        <v>0.05736754966887417</v>
       </c>
       <c r="R5">
-        <v>0.08249641319942611</v>
+        <v>0.09166666666666667</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1005,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>695.2</v>
+        <v>564.6</v>
       </c>
       <c r="V5">
-        <v>1.91304347826087</v>
+        <v>4.673841059602649</v>
       </c>
       <c r="W5">
-        <v>0.2648679460383812</v>
+        <v>0.1583577712609971</v>
       </c>
       <c r="X5">
-        <v>0.1665639773350055</v>
+        <v>0.2649795812159556</v>
       </c>
       <c r="Y5">
-        <v>0.09830396870337571</v>
+        <v>-0.1066218099549585</v>
       </c>
       <c r="Z5">
-        <v>0.8221361876565705</v>
+        <v>0.3136963941237572</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1346147759630016</v>
+        <v>0.1261602104431986</v>
       </c>
       <c r="AC5">
-        <v>-0.1346147759630016</v>
+        <v>-0.1261602104431986</v>
       </c>
       <c r="AD5">
-        <v>591.5</v>
+        <v>497.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>591.5</v>
+        <v>497.4</v>
       </c>
       <c r="AG5">
-        <v>-103.7</v>
+        <v>-67.20000000000005</v>
       </c>
       <c r="AH5">
-        <v>0.6194365902188711</v>
+        <v>0.8045939825299256</v>
       </c>
       <c r="AI5">
-        <v>0.5888501742160279</v>
+        <v>0.5846949570941576</v>
       </c>
       <c r="AJ5">
-        <v>-0.3993068925683484</v>
+        <v>-1.253731343283584</v>
       </c>
       <c r="AK5">
-        <v>-0.3352731975428389</v>
+        <v>-0.2348829080741001</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1070,120 +1067,608 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Access Holdings Plc (NGSE:ACCESSCORP)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.424</v>
+      </c>
+      <c r="E6">
+        <v>0.465</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>484.2</v>
+      </c>
+      <c r="L6">
+        <v>0.3576335032129404</v>
+      </c>
+      <c r="M6">
+        <v>44.982</v>
+      </c>
+      <c r="N6">
+        <v>0.08437816544738322</v>
+      </c>
+      <c r="O6">
+        <v>0.09289962825278811</v>
+      </c>
+      <c r="P6">
+        <v>44.5</v>
+      </c>
+      <c r="Q6">
+        <v>0.08347401988369911</v>
+      </c>
+      <c r="R6">
+        <v>0.09190417182982238</v>
+      </c>
+      <c r="S6">
+        <v>0.4819999999999993</v>
+      </c>
+      <c r="T6">
+        <v>0.0107153972700191</v>
+      </c>
+      <c r="U6">
+        <v>3315.3</v>
+      </c>
+      <c r="V6">
+        <v>6.218908272369162</v>
+      </c>
+      <c r="W6">
+        <v>0.237679167484783</v>
+      </c>
+      <c r="X6">
+        <v>0.2742781963798216</v>
+      </c>
+      <c r="Y6">
+        <v>-0.03659902889503858</v>
+      </c>
+      <c r="Z6">
+        <v>0.5100779866631504</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.1264153939086678</v>
+      </c>
+      <c r="AC6">
+        <v>-0.1264153939086678</v>
+      </c>
+      <c r="AD6">
+        <v>2320.5</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2320.5</v>
+      </c>
+      <c r="AG6">
+        <v>-994.8000000000002</v>
+      </c>
+      <c r="AH6">
+        <v>0.813183347350715</v>
+      </c>
+      <c r="AI6">
+        <v>0.5395256916996047</v>
+      </c>
+      <c r="AJ6">
+        <v>2.154645873944119</v>
+      </c>
+      <c r="AK6">
+        <v>-1.009232017855332</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>United Bank for Africa Plc (NGSE:UBA)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.414</v>
+      </c>
+      <c r="E7">
+        <v>0.472</v>
+      </c>
+      <c r="F7">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>397</v>
+      </c>
+      <c r="L7">
+        <v>0.3489496352289707</v>
+      </c>
+      <c r="M7">
+        <v>57.5</v>
+      </c>
+      <c r="N7">
+        <v>0.07619931089318845</v>
+      </c>
+      <c r="O7">
+        <v>0.1448362720403023</v>
+      </c>
+      <c r="P7">
+        <v>57.5</v>
+      </c>
+      <c r="Q7">
+        <v>0.07619931089318845</v>
+      </c>
+      <c r="R7">
+        <v>0.1448362720403023</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2761.6</v>
+      </c>
+      <c r="V7">
+        <v>3.659687251523986</v>
+      </c>
+      <c r="W7">
+        <v>0.1797030599311968</v>
+      </c>
+      <c r="X7">
+        <v>0.1381045415434188</v>
+      </c>
+      <c r="Y7">
+        <v>0.04159851838777801</v>
+      </c>
+      <c r="Z7">
+        <v>1.126658744305803</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.1271083997078812</v>
+      </c>
+      <c r="AC7">
+        <v>-0.1271083997078812</v>
+      </c>
+      <c r="AD7">
+        <v>684.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>684.5</v>
+      </c>
+      <c r="AG7">
+        <v>-2077.1</v>
+      </c>
+      <c r="AH7">
+        <v>0.475644500034744</v>
+      </c>
+      <c r="AI7">
+        <v>0.2413866064816448</v>
+      </c>
+      <c r="AJ7">
+        <v>1.570586011342155</v>
+      </c>
+      <c r="AK7">
+        <v>-28.03103913630233</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FBN Holdings Plc (NGSE:FBNH)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.355</v>
+      </c>
+      <c r="E8">
+        <v>0.5670000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>361</v>
+      </c>
+      <c r="L8">
+        <v>0.3773782145097219</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>2783.2</v>
+      </c>
+      <c r="V8">
+        <v>4.258913542463657</v>
+      </c>
+      <c r="W8">
+        <v>0.2071617123837943</v>
+      </c>
+      <c r="X8">
+        <v>0.1651548323439263</v>
+      </c>
+      <c r="Y8">
+        <v>0.04200688003986808</v>
+      </c>
+      <c r="Z8">
+        <v>1.44939393939394</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.1343444522472368</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1343444522472368</v>
+      </c>
+      <c r="AD8">
+        <v>1040.1</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1040.1</v>
+      </c>
+      <c r="AG8">
+        <v>-1743.1</v>
+      </c>
+      <c r="AH8">
+        <v>0.6141355692017005</v>
+      </c>
+      <c r="AI8">
+        <v>0.4004234841193455</v>
+      </c>
+      <c r="AJ8">
+        <v>1.599761380323054</v>
+      </c>
+      <c r="AK8">
+        <v>9.386645126548204</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fidelity Bank Plc (NGSE:FIDELITYBK)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.411</v>
+      </c>
+      <c r="E9">
+        <v>0.573</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>139.4</v>
+      </c>
+      <c r="L9">
+        <v>0.3861495844875347</v>
+      </c>
+      <c r="M9">
+        <v>11.5</v>
+      </c>
+      <c r="N9">
+        <v>0.03164556962025317</v>
+      </c>
+      <c r="O9">
+        <v>0.08249641319942611</v>
+      </c>
+      <c r="P9">
+        <v>11.5</v>
+      </c>
+      <c r="Q9">
+        <v>0.03164556962025317</v>
+      </c>
+      <c r="R9">
+        <v>0.08249641319942611</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>695.2</v>
+      </c>
+      <c r="V9">
+        <v>1.91304347826087</v>
+      </c>
+      <c r="W9">
+        <v>0.2648679460383812</v>
+      </c>
+      <c r="X9">
+        <v>0.1665814529555296</v>
+      </c>
+      <c r="Y9">
+        <v>0.09828649308285156</v>
+      </c>
+      <c r="Z9">
+        <v>0.8221361876565705</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.1346214265447363</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1346214265447363</v>
+      </c>
+      <c r="AD9">
+        <v>591.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>591.5</v>
+      </c>
+      <c r="AG9">
+        <v>-103.7</v>
+      </c>
+      <c r="AH9">
+        <v>0.6194365902188711</v>
+      </c>
+      <c r="AI9">
+        <v>0.5888501742160279</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.3993068925683484</v>
+      </c>
+      <c r="AK9">
+        <v>-0.3352731975428389</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Zenith Bank Plc (NGSE:ZENITHBANK)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D10">
         <v>0.351</v>
       </c>
-      <c r="E6">
+      <c r="E10">
         <v>0.398</v>
       </c>
-      <c r="F6">
+      <c r="F10">
         <v>0.137</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>641.7</v>
       </c>
-      <c r="L6">
+      <c r="L10">
         <v>0.508035784973478</v>
       </c>
-      <c r="M6">
+      <c r="M10">
         <v>84.8</v>
       </c>
-      <c r="N6">
+      <c r="N10">
         <v>0.09146801855247545</v>
       </c>
-      <c r="O6">
+      <c r="O10">
         <v>0.132148979273804</v>
       </c>
-      <c r="P6">
+      <c r="P10">
         <v>84.8</v>
       </c>
-      <c r="Q6">
+      <c r="Q10">
         <v>0.09146801855247545</v>
       </c>
-      <c r="R6">
+      <c r="R10">
         <v>0.132148979273804</v>
       </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
         <v>1704.2</v>
       </c>
-      <c r="V6">
+      <c r="V10">
         <v>1.838205155862366</v>
       </c>
-      <c r="W6">
+      <c r="W10">
         <v>0.2610234298730882</v>
       </c>
-      <c r="X6">
-        <v>0.1751765741414752</v>
-      </c>
-      <c r="Y6">
-        <v>0.08584685573161299</v>
-      </c>
-      <c r="Z6">
+      <c r="X10">
+        <v>0.1751952960812813</v>
+      </c>
+      <c r="Y10">
+        <v>0.08582813379180687</v>
+      </c>
+      <c r="Z10">
         <v>0.6747329059829061</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.1361378899982333</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1361378899982333</v>
-      </c>
-      <c r="AD6">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.1361444691470447</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1361444691470447</v>
+      </c>
+      <c r="AD10">
         <v>1711.1</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>1711.1</v>
       </c>
-      <c r="AG6">
+      <c r="AG10">
         <v>6.899999999999864</v>
       </c>
-      <c r="AH6">
+      <c r="AH10">
         <v>0.6485861572284133</v>
       </c>
-      <c r="AI6">
+      <c r="AI10">
         <v>0.4483544701813227</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ10">
         <v>0.007387580299785722</v>
       </c>
-      <c r="AK6">
+      <c r="AK10">
         <v>0.003266736104535491</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
         <v>0</v>
       </c>
     </row>
